--- a/astro-site/public/dl/kit-gestion-personal/04-onboarding-nuevo-empleado.xlsx
+++ b/astro-site/public/dl/kit-gestion-personal/04-onboarding-nuevo-empleado.xlsx
@@ -1,16 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Checklist Onboarding" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checklist Onboarding" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Checklist Onboarding'!$6:$6</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -18,10 +20,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt formatCode="DD/MM/YYYY" numFmtId="164"/>
-    <numFmt formatCode="0.0&quot;%&quot;" numFmtId="165"/>
+    <numFmt numFmtId="164" formatCode="DD/MM/YYYY"/>
+    <numFmt numFmtId="165" formatCode="0.0&quot;%&quot;"/>
   </numFmts>
-  <fonts count="13">
+  <fonts count="14">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -94,6 +96,11 @@
       <color rgb="00999999"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -163,58 +170,69 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="1" fillId="2" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="3" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="25">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="4" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="0" numFmtId="164" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="10" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="5" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="2" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="6" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="7" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="11" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="1" fillId="0" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="1" fillId="0" fontId="11" numFmtId="165" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="12" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="11" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" hidden="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium9"/>
+  <dxfs count="1">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00C8E6C9"/>
+          <bgColor rgb="00C8E6C9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -574,15 +592,16 @@
   <sheetPr>
     <tabColor rgb="00FFD700"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:B15"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="3"/>
-    <col customWidth="1" max="2" min="2" width="80"/>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="80" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -590,6 +609,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
         <is>
@@ -625,9 +645,7 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="B9" t="inlineStr"/>
-    </row>
+    <row r="9"/>
     <row r="10">
       <c r="B10" s="2" t="inlineStr">
         <is>
@@ -670,8 +688,25 @@
         </is>
       </c>
     </row>
+    <row r="16"/>
+    <row r="17">
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-gestion-personal · info@aichef.pro</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -680,18 +715,18 @@
   <sheetPr>
     <tabColor rgb="00FF6F00"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="5"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="16"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="16"/>
-    <col customWidth="1" max="6" min="6" width="12"/>
-    <col customWidth="1" max="7" min="7" width="20"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -722,6 +757,7 @@
       </c>
       <c r="E3" s="7" t="n"/>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="8" t="inlineStr">
         <is>
@@ -956,6 +992,7 @@
       <c r="F16" s="14" t="n"/>
       <c r="G16" s="15" t="n"/>
     </row>
+    <row r="17"/>
     <row r="18">
       <c r="A18" s="8" t="inlineStr">
         <is>
@@ -1152,6 +1189,7 @@
       <c r="F27" s="14" t="n"/>
       <c r="G27" s="15" t="n"/>
     </row>
+    <row r="28"/>
     <row r="29">
       <c r="A29" s="8" t="inlineStr">
         <is>
@@ -1367,6 +1405,7 @@
       <c r="F39" s="14" t="n"/>
       <c r="G39" s="15" t="n"/>
     </row>
+    <row r="40"/>
     <row r="41">
       <c r="A41" s="8" t="inlineStr">
         <is>
@@ -1639,6 +1678,7 @@
       <c r="F54" s="14" t="n"/>
       <c r="G54" s="15" t="n"/>
     </row>
+    <row r="55"/>
     <row r="56">
       <c r="A56" s="8" t="inlineStr">
         <is>
@@ -1835,6 +1875,26 @@
       <c r="F65" s="14" t="n"/>
       <c r="G65" s="15" t="n"/>
     </row>
+    <row r="66">
+      <c r="B66" s="24" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="C66">
+        <f>COUNTIF(F7:F65,"✓")</f>
+        <v>4.0</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="E66">
+        <f>COUNTIF(B7:B65,"?*")</f>
+        <v>51.0</v>
+      </c>
+    </row>
     <row r="67">
       <c r="A67" s="8" t="inlineStr">
         <is>
@@ -1850,7 +1910,7 @@
       </c>
       <c r="C68" s="20">
         <f>COUNTIF(F6:F66,"✓")</f>
-        <v/>
+        <v>5.0</v>
       </c>
     </row>
     <row r="69">
@@ -1871,9 +1931,10 @@
       </c>
       <c r="C70" s="22">
         <f>IF(68&gt;0,68/69*100,0)</f>
-        <v/>
-      </c>
-    </row>
+        <v>98.55072463768117</v>
+      </c>
+    </row>
+    <row r="71"/>
     <row r="72">
       <c r="A72" s="23" t="inlineStr">
         <is>
@@ -1900,11 +1961,25 @@
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="A29:G29"/>
   </mergeCells>
+  <conditionalFormatting sqref="A7:G65">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$F7="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="F7 F8 F9 F10 F11 F12 F13 F14 F15 F16 F20 F21 F22 F23 F24 F25 F26 F27 F31 F32 F33 F34 F35 F36 F37 F38 F39 F43 F44 F45 F46 F47 F48 F49 F50 F51 F52 F53 F54 F58 F59 F60 F61 F62 F63 F64 F65" type="list">
+    <dataValidation sqref="F7 F8 F9 F10 F11 F12 F13 F14 F15 F16 F20 F21 F22 F23 F24 F25 F26 F27 F31 F32 F33 F34 F35 F36 F37 F38 F39 F43 F44 F45 F46 F47 F48 F49 F50 F51 F52 F53 F54 F58 F59 F60 F61 F62 F63 F64 F65" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"✓,✗,—"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
--- a/astro-site/public/dl/kit-gestion-personal/04-onboarding-nuevo-empleado.xlsx
+++ b/astro-site/public/dl/kit-gestion-personal/04-onboarding-nuevo-empleado.xlsx
@@ -1,18 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checklist Onboarding" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Checklist Onboarding" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Checklist Onboarding'!$6:$6</definedName>
-  </definedNames>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -20,10 +18,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="DD/MM/YYYY"/>
-    <numFmt numFmtId="165" formatCode="0.0&quot;%&quot;"/>
+    <numFmt formatCode="DD/MM/YYYY" numFmtId="164"/>
+    <numFmt formatCode="0.0&quot;%&quot;" numFmtId="165"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="13">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -96,11 +94,6 @@
       <color rgb="00999999"/>
       <sz val="9"/>
     </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <sz val="10"/>
-    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -170,69 +163,58 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="24">
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="1" fillId="2" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf applyAlignment="1" borderId="1" fillId="3" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="1" fillId="0" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="1" fillId="0" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="1" fillId="4" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf borderId="1" fillId="2" fontId="0" numFmtId="164" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf applyAlignment="1" borderId="1" fillId="0" fontId="10" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="1" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="1" fillId="5" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="1" fillId="2" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="1" fillId="6" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="1" fillId="7" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="11" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="1" fillId="0" fontId="11" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="1" fillId="0" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="1" fillId="0" fontId="11" numFmtId="165" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="0" fillId="0" fontId="12" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle builtinId="0" hidden="0" name="Normal" xfId="0"/>
   </cellStyles>
-  <dxfs count="1">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="00C8E6C9"/>
-          <bgColor rgb="00C8E6C9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium9"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -592,16 +574,15 @@
   <sheetPr>
     <tabColor rgb="00FFD700"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
+    <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B17"/>
+  <dimension ref="B2:B15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="3" customWidth="1" min="1" max="1"/>
-    <col width="80" customWidth="1" min="2" max="2"/>
+    <col customWidth="1" max="1" min="1" width="3"/>
+    <col customWidth="1" max="2" min="2" width="80"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -609,7 +590,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
         <is>
@@ -645,7 +625,9 @@
         </is>
       </c>
     </row>
-    <row r="9"/>
+    <row r="9">
+      <c r="B9" t="inlineStr"/>
+    </row>
     <row r="10">
       <c r="B10" s="2" t="inlineStr">
         <is>
@@ -688,25 +670,8 @@
         </is>
       </c>
     </row>
-    <row r="16"/>
-    <row r="17">
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-gestion-personal · info@aichef.pro</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
-  <headerFooter>
-    <oddHeader/>
-    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
+  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
 </worksheet>
 </file>
 
@@ -715,18 +680,18 @@
   <sheetPr>
     <tabColor rgb="00FF6F00"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:G73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="45" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
+    <col customWidth="1" max="1" min="1" width="5"/>
+    <col customWidth="1" max="2" min="2" width="45"/>
+    <col customWidth="1" max="3" min="3" width="16"/>
+    <col customWidth="1" max="4" min="4" width="18"/>
+    <col customWidth="1" max="5" min="5" width="16"/>
+    <col customWidth="1" max="6" min="6" width="12"/>
+    <col customWidth="1" max="7" min="7" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -757,7 +722,6 @@
       </c>
       <c r="E3" s="7" t="n"/>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" s="8" t="inlineStr">
         <is>
@@ -992,7 +956,6 @@
       <c r="F16" s="14" t="n"/>
       <c r="G16" s="15" t="n"/>
     </row>
-    <row r="17"/>
     <row r="18">
       <c r="A18" s="8" t="inlineStr">
         <is>
@@ -1189,7 +1152,6 @@
       <c r="F27" s="14" t="n"/>
       <c r="G27" s="15" t="n"/>
     </row>
-    <row r="28"/>
     <row r="29">
       <c r="A29" s="8" t="inlineStr">
         <is>
@@ -1405,7 +1367,6 @@
       <c r="F39" s="14" t="n"/>
       <c r="G39" s="15" t="n"/>
     </row>
-    <row r="40"/>
     <row r="41">
       <c r="A41" s="8" t="inlineStr">
         <is>
@@ -1678,7 +1639,6 @@
       <c r="F54" s="14" t="n"/>
       <c r="G54" s="15" t="n"/>
     </row>
-    <row r="55"/>
     <row r="56">
       <c r="A56" s="8" t="inlineStr">
         <is>
@@ -1875,26 +1835,6 @@
       <c r="F65" s="14" t="n"/>
       <c r="G65" s="15" t="n"/>
     </row>
-    <row r="66">
-      <c r="B66" s="24" t="inlineStr">
-        <is>
-          <t>Tareas completadas:</t>
-        </is>
-      </c>
-      <c r="C66">
-        <f>COUNTIF(F7:F65,"✓")</f>
-        <v>4.0</v>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>de</t>
-        </is>
-      </c>
-      <c r="E66">
-        <f>COUNTIF(B7:B65,"?*")</f>
-        <v>51.0</v>
-      </c>
-    </row>
     <row r="67">
       <c r="A67" s="8" t="inlineStr">
         <is>
@@ -1910,7 +1850,7 @@
       </c>
       <c r="C68" s="20">
         <f>COUNTIF(F6:F66,"✓")</f>
-        <v>5.0</v>
+        <v/>
       </c>
     </row>
     <row r="69">
@@ -1931,10 +1871,9 @@
       </c>
       <c r="C70" s="22">
         <f>IF(68&gt;0,68/69*100,0)</f>
-        <v>98.55072463768117</v>
-      </c>
-    </row>
-    <row r="71"/>
+        <v/>
+      </c>
+    </row>
     <row r="72">
       <c r="A72" s="23" t="inlineStr">
         <is>
@@ -1961,25 +1900,11 @@
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="A29:G29"/>
   </mergeCells>
-  <conditionalFormatting sqref="A7:G65">
-    <cfRule type="expression" priority="1" dxfId="0">
-      <formula>$F7="✓"</formula>
-    </cfRule>
-  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F7 F8 F9 F10 F11 F12 F13 F14 F15 F16 F20 F21 F22 F23 F24 F25 F26 F27 F31 F32 F33 F34 F35 F36 F37 F38 F39 F43 F44 F45 F46 F47 F48 F49 F50 F51 F52 F53 F54 F58 F59 F60 F61 F62 F63 F64 F65" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation allowBlank="1" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="F7 F8 F9 F10 F11 F12 F13 F14 F15 F16 F20 F21 F22 F23 F24 F25 F26 F27 F31 F32 F33 F34 F35 F36 F37 F38 F39 F43 F44 F45 F46 F47 F48 F49 F50 F51 F52 F53 F54 F58 F59 F60 F61 F62 F63 F64 F65" type="list">
       <formula1>"✓,✗,—"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
-  <headerFooter>
-    <oddHeader/>
-    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
+  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
 </worksheet>
 </file>
--- a/astro-site/public/dl/kit-gestion-personal/04-onboarding-nuevo-empleado.xlsx
+++ b/astro-site/public/dl/kit-gestion-personal/04-onboarding-nuevo-empleado.xlsx
@@ -1,16 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Checklist Onboarding" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checklist Onboarding" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Checklist Onboarding'!$6:$6</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -18,8 +20,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt formatCode="DD/MM/YYYY" numFmtId="164"/>
-    <numFmt formatCode="0.0&quot;%&quot;" numFmtId="165"/>
+    <numFmt numFmtId="164" formatCode="DD/MM/YYYY"/>
+    <numFmt numFmtId="165" formatCode="0.0&quot;%&quot;"/>
   </numFmts>
   <fonts count="13">
     <font>
@@ -163,58 +165,68 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="24">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="1" fillId="2" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="3" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="4" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="0" numFmtId="164" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="10" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="5" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="2" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="6" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="7" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="11" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="1" fillId="0" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="1" fillId="0" fontId="11" numFmtId="165" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="12" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="11" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" hidden="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium9"/>
+  <dxfs count="1">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00C8E6C9"/>
+          <bgColor rgb="00C8E6C9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -574,15 +586,16 @@
   <sheetPr>
     <tabColor rgb="00FFD700"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:B15"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="3"/>
-    <col customWidth="1" max="2" min="2" width="80"/>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="80" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -590,6 +603,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
         <is>
@@ -625,9 +639,7 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="B9" t="inlineStr"/>
-    </row>
+    <row r="9"/>
     <row r="10">
       <c r="B10" s="2" t="inlineStr">
         <is>
@@ -670,8 +682,25 @@
         </is>
       </c>
     </row>
+    <row r="16"/>
+    <row r="17">
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-gestion-personal · info@aichef.pro</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -680,18 +709,18 @@
   <sheetPr>
     <tabColor rgb="00FF6F00"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="5"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="16"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="16"/>
-    <col customWidth="1" max="6" min="6" width="12"/>
-    <col customWidth="1" max="7" min="7" width="20"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -722,6 +751,7 @@
       </c>
       <c r="E3" s="7" t="n"/>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="8" t="inlineStr">
         <is>
@@ -956,6 +986,7 @@
       <c r="F16" s="14" t="n"/>
       <c r="G16" s="15" t="n"/>
     </row>
+    <row r="17"/>
     <row r="18">
       <c r="A18" s="8" t="inlineStr">
         <is>
@@ -1152,6 +1183,7 @@
       <c r="F27" s="14" t="n"/>
       <c r="G27" s="15" t="n"/>
     </row>
+    <row r="28"/>
     <row r="29">
       <c r="A29" s="8" t="inlineStr">
         <is>
@@ -1367,6 +1399,7 @@
       <c r="F39" s="14" t="n"/>
       <c r="G39" s="15" t="n"/>
     </row>
+    <row r="40"/>
     <row r="41">
       <c r="A41" s="8" t="inlineStr">
         <is>
@@ -1639,6 +1672,7 @@
       <c r="F54" s="14" t="n"/>
       <c r="G54" s="15" t="n"/>
     </row>
+    <row r="55"/>
     <row r="56">
       <c r="A56" s="8" t="inlineStr">
         <is>
@@ -1835,6 +1869,7 @@
       <c r="F65" s="14" t="n"/>
       <c r="G65" s="15" t="n"/>
     </row>
+    <row r="66"/>
     <row r="67">
       <c r="A67" s="8" t="inlineStr">
         <is>
@@ -1849,8 +1884,17 @@
         </is>
       </c>
       <c r="C68" s="20">
-        <f>COUNTIF(F6:F66,"✓")</f>
-        <v/>
+        <f>COUNTIF(F7:F65,"✓")</f>
+        <v>4.0</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="E68">
+        <f>COUNTIF(B7:B65,"?*")</f>
+        <v>51.0</v>
       </c>
     </row>
     <row r="69">
@@ -1870,10 +1914,11 @@
         </is>
       </c>
       <c r="C70" s="22">
-        <f>IF(68&gt;0,68/69*100,0)</f>
-        <v/>
-      </c>
-    </row>
+        <f>IF(C69&gt;0,C68/C69*100,0)</f>
+        <v>8.51063829787234</v>
+      </c>
+    </row>
+    <row r="71"/>
     <row r="72">
       <c r="A72" s="23" t="inlineStr">
         <is>
@@ -1900,11 +1945,25 @@
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="A29:G29"/>
   </mergeCells>
+  <conditionalFormatting sqref="A7:G65">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$F7="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="F7 F8 F9 F10 F11 F12 F13 F14 F15 F16 F20 F21 F22 F23 F24 F25 F26 F27 F31 F32 F33 F34 F35 F36 F37 F38 F39 F43 F44 F45 F46 F47 F48 F49 F50 F51 F52 F53 F54 F58 F59 F60 F61 F62 F63 F64 F65" type="list">
+    <dataValidation sqref="F7 F8 F9 F10 F11 F12 F13 F14 F15 F16 F20 F21 F22 F23 F24 F25 F26 F27 F31 F32 F33 F34 F35 F36 F37 F38 F39 F43 F44 F45 F46 F47 F48 F49 F50 F51 F52 F53 F54 F58 F59 F60 F61 F62 F63 F64 F65" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"✓,✗,—"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
--- a/astro-site/public/dl/kit-gestion-personal/04-onboarding-nuevo-empleado.xlsx
+++ b/astro-site/public/dl/kit-gestion-personal/04-onboarding-nuevo-empleado.xlsx
@@ -11,7 +11,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checklist Onboarding" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Checklist Onboarding'!$6:$6</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Instrucciones'!$A$1:$B$36</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Checklist Onboarding'!$6:$6,'Checklist Onboarding'!$A:$B</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Checklist Onboarding'!$A$1:$H$76</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -19,11 +21,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="DD/MM/YYYY"/>
     <numFmt numFmtId="165" formatCode="0.0&quot;%&quot;"/>
+    <numFmt numFmtId="166" formatCode="dd/mm/yyyy"/>
+    <numFmt numFmtId="167" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="13">
+  <fonts count="16">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -96,8 +100,19 @@
       <color rgb="00999999"/>
       <sz val="9"/>
     </font>
+    <font>
+      <b val="1"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="14">
     <fill>
       <patternFill/>
     </fill>
@@ -140,6 +155,36 @@
         <bgColor rgb="00FFEBEE"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E3F2FD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF3E0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C8E6C9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F3E5F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFEBEE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8F5E9"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -167,7 +212,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -212,6 +257,60 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="11" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="11" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="11" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -588,7 +687,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -597,7 +696,7 @@
   <sheetData>
     <row r="1"/>
     <row r="2">
-      <c r="B2" s="1" t="inlineStr">
+      <c r="B2" s="24" t="inlineStr">
         <is>
           <t>04 · Onboarding Nuevo Empleado</t>
         </is>
@@ -605,88 +704,159 @@
     </row>
     <row r="3"/>
     <row r="4">
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="25" t="inlineStr">
         <is>
           <t>Cómo usar esta plantilla:</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>▸ Abre un checklist nuevo para cada incorporación.</t>
+      <c r="B5" s="26" t="inlineStr">
+        <is>
+          <t>▸ Duplica el fichero para cada incorporación y escribe arriba el nombre, el puesto y la fecha de alta.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>▸ Asigna un responsable a cada tarea y establece fecha límite.</t>
+      <c r="B6" s="26" t="inlineStr">
+        <is>
+          <t>▸ Marca cada tarea en la columna «Hecho»: ✓ hecha · ✗ pendiente · — no aplica a este puesto.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>▸ Marca ✓ cuando se complete cada paso.</t>
+      <c r="B7" s="26" t="inlineStr">
+        <is>
+          <t>▸ La «—» es importante: saca la tarea del denominador. Un cocinero de partida que no necesita el acceso al TPV puede llegar al 100 % igual que un jefe de sala.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>▸ Revisa el checklist completo antes de finalizar el periodo de prueba.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9"/>
+      <c r="B8" s="26" t="inlineStr">
+        <is>
+          <t>▸ Son DOS columnas: «Plazo» dice cuándo vence la tarea contando días desde el alta (Día -1 es ANTES de que empiece a trabajar) y «Fecha límite» te da el día real, calculado a partir de la fecha de alta que escribas arriba. Escribe esa fecha y la columna entera se rellena sola; así puedes ordenar el checklist por vencimiento.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="27" t="inlineStr">
+        <is>
+          <t>▸ El resumen del final cuenta tramo a tramo, así que las cabeceras de sección ya no se cuelan como tareas hechas: un checklist en blanco marca 0 %.</t>
+        </is>
+      </c>
+    </row>
     <row r="10">
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>Categorías:</t>
-        </is>
-      </c>
+      <c r="B10" s="2" t="n"/>
     </row>
     <row r="11">
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="26" t="inlineStr">
+        <is>
+          <t>Categorías (cada sección lleva su color):</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="26" t="inlineStr">
         <is>
           <t>▸ Azul = Documentación legal y administrativa</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="B12" s="3" t="inlineStr">
+    <row r="13">
+      <c r="B13" s="26" t="inlineStr">
         <is>
           <t>▸ Naranja = Formación obligatoria</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="B13" s="3" t="inlineStr">
+    <row r="14">
+      <c r="B14" s="26" t="inlineStr">
         <is>
           <t>▸ Verde = Equipamiento y accesos</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="B14" s="3" t="inlineStr">
+    <row r="15">
+      <c r="B15" s="26" t="inlineStr">
         <is>
           <t>▸ Morado = Formación operativa</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="B15" s="3" t="inlineStr">
+    <row r="16">
+      <c r="B16" s="27" t="inlineStr">
         <is>
           <t>▸ Rojo = Periodo de prueba y evaluación</t>
         </is>
       </c>
     </row>
-    <row r="16"/>
     <row r="17">
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-gestion-personal · info@aichef.pro</t>
+      <c r="B17" s="3" t="n"/>
+    </row>
+    <row r="18">
+      <c r="B18" s="27" t="inlineStr">
+        <is>
+          <t>Plazos que no dependen de ti:</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="27" t="inlineStr">
+        <is>
+          <t>▸ El alta en la Seguridad Social tiene que estar presentada ANTES del inicio de la jornada (art. 32.3 del RD 84/1996). No es papeleo del primer día: es requisito para que ese primer día sea legal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="27" t="inlineStr">
+        <is>
+          <t>▸ El contrato se comunica a Contrat@ (SEPE) dentro de los 10 días hábiles siguientes a su formalización, y la copia básica va a la representación legal de los trabajadores en 10 días.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="27" t="inlineStr">
+        <is>
+          <t>▸ El modelo 145 lo firma la persona para que puedas calcular bien su retención de IRPF; sin él, la retención se aplica sin cargas familiares.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22"/>
+    <row r="23">
+      <c r="B23" s="27" t="inlineStr">
+        <is>
+          <t>Aviso: los plazos son los del Estatuto de los Trabajadores y su normativa de desarrollo a agosto de 2026. Tu convenio puede exigir más trámites, nunca menos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24"/>
+    <row r="25"/>
+    <row r="26"/>
+    <row r="27"/>
+    <row r="28"/>
+    <row r="29"/>
+    <row r="30"/>
+    <row r="31"/>
+    <row r="32"/>
+    <row r="33"/>
+    <row r="34">
+      <c r="B34" s="27" t="inlineStr">
+        <is>
+          <t>Para editar una celda bloqueada: Revisar → Desproteger hoja (no tiene contraseña). Las celdas verdes ya son editables sin desproteger nada.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="27" t="inlineStr">
+        <is>
+          <t>Diseñado por John Guerrero — chef y consultor gastronómico desde 2010, en cocina desde los 17 años · johnguerrero.es</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="27" t="inlineStr">
+        <is>
+          <t>Versión 2.0 · agosto 2026 · aichef.pro/kit-gestion-personal · info@aichef.pro</t>
         </is>
       </c>
     </row>
@@ -711,16 +881,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G73"/>
+  <dimension ref="A1:H76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="45" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="52" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -743,21 +914,28 @@
           <t>Puesto:</t>
         </is>
       </c>
-      <c r="B3" s="7" t="n"/>
+      <c r="B3" s="28" t="n"/>
       <c r="D3" s="6" t="inlineStr">
         <is>
           <t>Fecha alta:</t>
         </is>
       </c>
-      <c r="E3" s="7" t="n"/>
+      <c r="E3" s="28" t="n"/>
     </row>
     <row r="4"/>
     <row r="5">
-      <c r="A5" s="8" t="inlineStr">
+      <c r="A5" s="29" t="inlineStr">
         <is>
           <t>📋 DOCUMENTACIÓN LEGAL Y ADMINISTRATIVA</t>
         </is>
       </c>
+      <c r="B5" s="30" t="n"/>
+      <c r="C5" s="30" t="n"/>
+      <c r="D5" s="30" t="n"/>
+      <c r="E5" s="30" t="n"/>
+      <c r="F5" s="30" t="n"/>
+      <c r="G5" s="30" t="n"/>
+      <c r="H5" s="30" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="9" t="inlineStr">
@@ -782,17 +960,22 @@
       </c>
       <c r="E6" s="9" t="inlineStr">
         <is>
-          <t>Fecha Límite</t>
+          <t>Plazo</t>
         </is>
       </c>
       <c r="F6" s="9" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>Hecho</t>
         </is>
       </c>
       <c r="G6" s="9" t="inlineStr">
         <is>
           <t>Notas</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Fecha límite</t>
         </is>
       </c>
     </row>
@@ -807,13 +990,21 @@
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">DOCUMENTACIÓN </t>
-        </is>
-      </c>
-      <c r="D7" s="7" t="n"/>
-      <c r="E7" s="13" t="n"/>
-      <c r="F7" s="14" t="n"/>
-      <c r="G7" s="15" t="n"/>
+          <t>DOCUMENTACIÓN LEGAL</t>
+        </is>
+      </c>
+      <c r="D7" s="28" t="n"/>
+      <c r="E7" s="31" t="inlineStr">
+        <is>
+          <t>Día -1</t>
+        </is>
+      </c>
+      <c r="F7" s="32" t="n"/>
+      <c r="G7" s="33" t="n"/>
+      <c r="H7" s="34">
+        <f>IF($E$3="","",$E$3+-1)</f>
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="10" t="n">
@@ -826,13 +1017,21 @@
       </c>
       <c r="C8" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">DOCUMENTACIÓN </t>
-        </is>
-      </c>
-      <c r="D8" s="7" t="n"/>
-      <c r="E8" s="13" t="n"/>
-      <c r="F8" s="14" t="n"/>
-      <c r="G8" s="15" t="n"/>
+          <t>DOCUMENTACIÓN LEGAL</t>
+        </is>
+      </c>
+      <c r="D8" s="28" t="n"/>
+      <c r="E8" s="31" t="inlineStr">
+        <is>
+          <t>Día -1</t>
+        </is>
+      </c>
+      <c r="F8" s="32" t="n"/>
+      <c r="G8" s="33" t="n"/>
+      <c r="H8" s="34">
+        <f>IF($E$3="","",$E$3+-1)</f>
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="10" t="n">
@@ -845,13 +1044,21 @@
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">DOCUMENTACIÓN </t>
-        </is>
-      </c>
-      <c r="D9" s="7" t="n"/>
-      <c r="E9" s="13" t="n"/>
-      <c r="F9" s="14" t="n"/>
-      <c r="G9" s="15" t="n"/>
+          <t>DOCUMENTACIÓN LEGAL</t>
+        </is>
+      </c>
+      <c r="D9" s="28" t="n"/>
+      <c r="E9" s="31" t="inlineStr">
+        <is>
+          <t>Día -1</t>
+        </is>
+      </c>
+      <c r="F9" s="32" t="n"/>
+      <c r="G9" s="33" t="n"/>
+      <c r="H9" s="34">
+        <f>IF($E$3="","",$E$3+-1)</f>
+        <v/>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="10" t="n">
@@ -859,18 +1066,26 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>Alta en Seguridad Social (TA.2/S)</t>
+          <t>Alta en Seguridad Social (TA.2/S) — OBLIGATORIO ANTES del inicio de la jornada (art. 32.3 RD 84/1996)</t>
         </is>
       </c>
       <c r="C10" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">DOCUMENTACIÓN </t>
-        </is>
-      </c>
-      <c r="D10" s="7" t="n"/>
-      <c r="E10" s="13" t="n"/>
-      <c r="F10" s="14" t="n"/>
-      <c r="G10" s="15" t="n"/>
+          <t>DOCUMENTACIÓN LEGAL</t>
+        </is>
+      </c>
+      <c r="D10" s="28" t="n"/>
+      <c r="E10" s="31" t="inlineStr">
+        <is>
+          <t>Día -1</t>
+        </is>
+      </c>
+      <c r="F10" s="32" t="n"/>
+      <c r="G10" s="33" t="n"/>
+      <c r="H10" s="34">
+        <f>IF($E$3="","",$E$3+-1)</f>
+        <v/>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="10" t="n">
@@ -883,13 +1098,21 @@
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">DOCUMENTACIÓN </t>
-        </is>
-      </c>
-      <c r="D11" s="7" t="n"/>
-      <c r="E11" s="13" t="n"/>
-      <c r="F11" s="14" t="n"/>
-      <c r="G11" s="15" t="n"/>
+          <t>DOCUMENTACIÓN LEGAL</t>
+        </is>
+      </c>
+      <c r="D11" s="28" t="n"/>
+      <c r="E11" s="31" t="inlineStr">
+        <is>
+          <t>Día 1</t>
+        </is>
+      </c>
+      <c r="F11" s="32" t="n"/>
+      <c r="G11" s="33" t="n"/>
+      <c r="H11" s="34">
+        <f>IF($E$3="","",$E$3+1)</f>
+        <v/>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="10" t="n">
@@ -902,13 +1125,21 @@
       </c>
       <c r="C12" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">DOCUMENTACIÓN </t>
-        </is>
-      </c>
-      <c r="D12" s="7" t="n"/>
-      <c r="E12" s="13" t="n"/>
-      <c r="F12" s="14" t="n"/>
-      <c r="G12" s="15" t="n"/>
+          <t>DOCUMENTACIÓN LEGAL</t>
+        </is>
+      </c>
+      <c r="D12" s="28" t="n"/>
+      <c r="E12" s="31" t="inlineStr">
+        <is>
+          <t>Día 1</t>
+        </is>
+      </c>
+      <c r="F12" s="32" t="n"/>
+      <c r="G12" s="33" t="n"/>
+      <c r="H12" s="34">
+        <f>IF($E$3="","",$E$3+1)</f>
+        <v/>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="10" t="n">
@@ -921,13 +1152,21 @@
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">DOCUMENTACIÓN </t>
-        </is>
-      </c>
-      <c r="D13" s="7" t="n"/>
-      <c r="E13" s="13" t="n"/>
-      <c r="F13" s="14" t="n"/>
-      <c r="G13" s="15" t="n"/>
+          <t>DOCUMENTACIÓN LEGAL</t>
+        </is>
+      </c>
+      <c r="D13" s="28" t="n"/>
+      <c r="E13" s="31" t="inlineStr">
+        <is>
+          <t>Día 1</t>
+        </is>
+      </c>
+      <c r="F13" s="32" t="n"/>
+      <c r="G13" s="33" t="n"/>
+      <c r="H13" s="34">
+        <f>IF($E$3="","",$E$3+1)</f>
+        <v/>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="10" t="n">
@@ -940,13 +1179,21 @@
       </c>
       <c r="C14" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">DOCUMENTACIÓN </t>
-        </is>
-      </c>
-      <c r="D14" s="7" t="n"/>
-      <c r="E14" s="13" t="n"/>
-      <c r="F14" s="14" t="n"/>
-      <c r="G14" s="15" t="n"/>
+          <t>DOCUMENTACIÓN LEGAL</t>
+        </is>
+      </c>
+      <c r="D14" s="28" t="n"/>
+      <c r="E14" s="31" t="inlineStr">
+        <is>
+          <t>Día 1</t>
+        </is>
+      </c>
+      <c r="F14" s="32" t="n"/>
+      <c r="G14" s="33" t="n"/>
+      <c r="H14" s="34">
+        <f>IF($E$3="","",$E$3+1)</f>
+        <v/>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="10" t="n">
@@ -959,13 +1206,21 @@
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">DOCUMENTACIÓN </t>
-        </is>
-      </c>
-      <c r="D15" s="7" t="n"/>
-      <c r="E15" s="13" t="n"/>
-      <c r="F15" s="14" t="n"/>
-      <c r="G15" s="15" t="n"/>
+          <t>DOCUMENTACIÓN LEGAL</t>
+        </is>
+      </c>
+      <c r="D15" s="28" t="n"/>
+      <c r="E15" s="31" t="inlineStr">
+        <is>
+          <t>Día 1</t>
+        </is>
+      </c>
+      <c r="F15" s="32" t="n"/>
+      <c r="G15" s="33" t="n"/>
+      <c r="H15" s="34">
+        <f>IF($E$3="","",$E$3+1)</f>
+        <v/>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="10" t="n">
@@ -978,980 +1233,1415 @@
       </c>
       <c r="C16" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">DOCUMENTACIÓN </t>
-        </is>
-      </c>
-      <c r="D16" s="7" t="n"/>
-      <c r="E16" s="13" t="n"/>
-      <c r="F16" s="14" t="n"/>
-      <c r="G16" s="15" t="n"/>
-    </row>
-    <row r="17"/>
+          <t>DOCUMENTACIÓN LEGAL</t>
+        </is>
+      </c>
+      <c r="D16" s="28" t="n"/>
+      <c r="E16" s="31" t="inlineStr">
+        <is>
+          <t>Día 7</t>
+        </is>
+      </c>
+      <c r="F16" s="32" t="n"/>
+      <c r="G16" s="33" t="n"/>
+      <c r="H16" s="34">
+        <f>IF($E$3="","",$E$3+7)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>11</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Comunicación del contrato a Contrat@ (SEPE) — 10 días hábiles desde la firma</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>DOCUMENTACIÓN LEGAL</t>
+        </is>
+      </c>
+      <c r="D17" s="35" t="n"/>
+      <c r="E17" s="36" t="inlineStr">
+        <is>
+          <t>Día 7</t>
+        </is>
+      </c>
+      <c r="F17" s="35" t="n"/>
+      <c r="G17" s="35" t="n"/>
+      <c r="H17" s="34">
+        <f>IF($E$3="","",$E$3+7)</f>
+        <v/>
+      </c>
+    </row>
     <row r="18">
-      <c r="A18" s="8" t="inlineStr">
+      <c r="A18" t="n">
+        <v>12</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Copia básica del contrato a la representación legal de los trabajadores (RLT) — 10 días</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>DOCUMENTACIÓN LEGAL</t>
+        </is>
+      </c>
+      <c r="D18" s="35" t="n"/>
+      <c r="E18" s="36" t="inlineStr">
+        <is>
+          <t>Día 7</t>
+        </is>
+      </c>
+      <c r="F18" s="35" t="n"/>
+      <c r="G18" s="35" t="n"/>
+      <c r="H18" s="34">
+        <f>IF($E$3="","",$E$3+7)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>13</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Modelo 145 de IRPF firmado (situación personal y familiar para calcular la retención)</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>DOCUMENTACIÓN LEGAL</t>
+        </is>
+      </c>
+      <c r="D19" s="35" t="n"/>
+      <c r="E19" s="36" t="inlineStr">
+        <is>
+          <t>Día 1</t>
+        </is>
+      </c>
+      <c r="F19" s="35" t="n"/>
+      <c r="G19" s="35" t="n"/>
+      <c r="H19" s="34">
+        <f>IF($E$3="","",$E$3+1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20"/>
+    <row r="21">
+      <c r="A21" s="37" t="inlineStr">
         <is>
           <t>🎓 FORMACIÓN OBLIGATORIA</t>
         </is>
       </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="9" t="inlineStr">
+      <c r="B21" s="38" t="n"/>
+      <c r="C21" s="38" t="n"/>
+      <c r="D21" s="38" t="n"/>
+      <c r="E21" s="38" t="n"/>
+      <c r="F21" s="38" t="n"/>
+      <c r="G21" s="38" t="n"/>
+      <c r="H21" s="38" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="9" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B19" s="9" t="inlineStr">
+      <c r="B22" s="9" t="inlineStr">
         <is>
           <t>Tarea</t>
         </is>
       </c>
-      <c r="C19" s="9" t="inlineStr">
+      <c r="C22" s="9" t="inlineStr">
         <is>
           <t>Categoría</t>
         </is>
       </c>
-      <c r="D19" s="9" t="inlineStr">
+      <c r="D22" s="9" t="inlineStr">
         <is>
           <t>Responsable</t>
         </is>
       </c>
-      <c r="E19" s="9" t="inlineStr">
-        <is>
-          <t>Fecha Límite</t>
-        </is>
-      </c>
-      <c r="F19" s="9" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="G19" s="9" t="inlineStr">
+      <c r="E22" s="9" t="inlineStr">
+        <is>
+          <t>Plazo</t>
+        </is>
+      </c>
+      <c r="F22" s="9" t="inlineStr">
+        <is>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="G22" s="9" t="inlineStr">
         <is>
           <t>Notas</t>
         </is>
       </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="B20" s="11" t="inlineStr">
-        <is>
-          <t>Carnet manipulador de alimentos vigente</t>
-        </is>
-      </c>
-      <c r="C20" s="16" t="inlineStr">
-        <is>
-          <t>FORMACIÓN OBLI</t>
-        </is>
-      </c>
-      <c r="D20" s="7" t="n"/>
-      <c r="E20" s="13" t="n"/>
-      <c r="F20" s="14" t="n"/>
-      <c r="G20" s="15" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="B21" s="11" t="inlineStr">
-        <is>
-          <t>Formación APPCC — protocolos del establecimiento</t>
-        </is>
-      </c>
-      <c r="C21" s="16" t="inlineStr">
-        <is>
-          <t>FORMACIÓN OBLI</t>
-        </is>
-      </c>
-      <c r="D21" s="7" t="n"/>
-      <c r="E21" s="13" t="n"/>
-      <c r="F21" s="14" t="n"/>
-      <c r="G21" s="15" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="B22" s="11" t="inlineStr">
-        <is>
-          <t>Formación alérgenos — los 14 alérgenos de declaración obligatoria</t>
-        </is>
-      </c>
-      <c r="C22" s="16" t="inlineStr">
-        <is>
-          <t>FORMACIÓN OBLI</t>
-        </is>
-      </c>
-      <c r="D22" s="7" t="n"/>
-      <c r="E22" s="13" t="n"/>
-      <c r="F22" s="14" t="n"/>
-      <c r="G22" s="15" t="n"/>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Fecha límite</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="10" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>PRL específica del puesto — riesgos y medidas preventivas</t>
+          <t>Carnet manipulador de alimentos vigente</t>
         </is>
       </c>
       <c r="C23" s="16" t="inlineStr">
         <is>
-          <t>FORMACIÓN OBLI</t>
-        </is>
-      </c>
-      <c r="D23" s="7" t="n"/>
-      <c r="E23" s="13" t="n"/>
-      <c r="F23" s="14" t="n"/>
-      <c r="G23" s="15" t="n"/>
+          <t>FORMACIÓN OBLIGATORIA</t>
+        </is>
+      </c>
+      <c r="D23" s="28" t="n"/>
+      <c r="E23" s="31" t="inlineStr">
+        <is>
+          <t>Día 1</t>
+        </is>
+      </c>
+      <c r="F23" s="32" t="n"/>
+      <c r="G23" s="33" t="n"/>
+      <c r="H23" s="34">
+        <f>IF($E$3="","",$E$3+1)</f>
+        <v/>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="10" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t>Plan de emergencia y evacuación — rutas y puntos de encuentro</t>
+          <t>Formación APPCC — protocolos del establecimiento</t>
         </is>
       </c>
       <c r="C24" s="16" t="inlineStr">
         <is>
-          <t>FORMACIÓN OBLI</t>
-        </is>
-      </c>
-      <c r="D24" s="7" t="n"/>
-      <c r="E24" s="13" t="n"/>
-      <c r="F24" s="14" t="n"/>
-      <c r="G24" s="15" t="n"/>
+          <t>FORMACIÓN OBLIGATORIA</t>
+        </is>
+      </c>
+      <c r="D24" s="28" t="n"/>
+      <c r="E24" s="31" t="inlineStr">
+        <is>
+          <t>Día 7</t>
+        </is>
+      </c>
+      <c r="F24" s="32" t="n"/>
+      <c r="G24" s="33" t="n"/>
+      <c r="H24" s="34">
+        <f>IF($E$3="","",$E$3+7)</f>
+        <v/>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="10" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t>Protocolo acoso laboral — información y canal de denuncia</t>
+          <t>Formación alérgenos — los 14 alérgenos de declaración obligatoria</t>
         </is>
       </c>
       <c r="C25" s="16" t="inlineStr">
         <is>
-          <t>FORMACIÓN OBLI</t>
-        </is>
-      </c>
-      <c r="D25" s="7" t="n"/>
-      <c r="E25" s="13" t="n"/>
-      <c r="F25" s="14" t="n"/>
-      <c r="G25" s="15" t="n"/>
+          <t>FORMACIÓN OBLIGATORIA</t>
+        </is>
+      </c>
+      <c r="D25" s="28" t="n"/>
+      <c r="E25" s="31" t="inlineStr">
+        <is>
+          <t>Día 7</t>
+        </is>
+      </c>
+      <c r="F25" s="32" t="n"/>
+      <c r="G25" s="33" t="n"/>
+      <c r="H25" s="34">
+        <f>IF($E$3="","",$E$3+7)</f>
+        <v/>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="10" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t>Normativa de uniformidad e higiene personal</t>
+          <t>PRL específica del puesto — riesgos y medidas preventivas</t>
         </is>
       </c>
       <c r="C26" s="16" t="inlineStr">
         <is>
-          <t>FORMACIÓN OBLI</t>
-        </is>
-      </c>
-      <c r="D26" s="7" t="n"/>
-      <c r="E26" s="13" t="n"/>
-      <c r="F26" s="14" t="n"/>
-      <c r="G26" s="15" t="n"/>
+          <t>FORMACIÓN OBLIGATORIA</t>
+        </is>
+      </c>
+      <c r="D26" s="28" t="n"/>
+      <c r="E26" s="31" t="inlineStr">
+        <is>
+          <t>Día 1</t>
+        </is>
+      </c>
+      <c r="F26" s="32" t="n"/>
+      <c r="G26" s="33" t="n"/>
+      <c r="H26" s="34">
+        <f>IF($E$3="","",$E$3+1)</f>
+        <v/>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="B27" s="11" t="inlineStr">
+        <is>
+          <t>Plan de emergencia y evacuación — rutas y puntos de encuentro</t>
+        </is>
+      </c>
+      <c r="C27" s="16" t="inlineStr">
+        <is>
+          <t>FORMACIÓN OBLIGATORIA</t>
+        </is>
+      </c>
+      <c r="D27" s="28" t="n"/>
+      <c r="E27" s="31" t="inlineStr">
+        <is>
+          <t>Día 7</t>
+        </is>
+      </c>
+      <c r="F27" s="32" t="n"/>
+      <c r="G27" s="33" t="n"/>
+      <c r="H27" s="34">
+        <f>IF($E$3="","",$E$3+7)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="B28" s="11" t="inlineStr">
+        <is>
+          <t>Protocolo acoso laboral — información y canal de denuncia</t>
+        </is>
+      </c>
+      <c r="C28" s="16" t="inlineStr">
+        <is>
+          <t>FORMACIÓN OBLIGATORIA</t>
+        </is>
+      </c>
+      <c r="D28" s="28" t="n"/>
+      <c r="E28" s="31" t="inlineStr">
+        <is>
+          <t>Día 7</t>
+        </is>
+      </c>
+      <c r="F28" s="32" t="n"/>
+      <c r="G28" s="33" t="n"/>
+      <c r="H28" s="34">
+        <f>IF($E$3="","",$E$3+7)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="B29" s="11" t="inlineStr">
+        <is>
+          <t>Normativa de uniformidad e higiene personal</t>
+        </is>
+      </c>
+      <c r="C29" s="16" t="inlineStr">
+        <is>
+          <t>FORMACIÓN OBLIGATORIA</t>
+        </is>
+      </c>
+      <c r="D29" s="28" t="n"/>
+      <c r="E29" s="31" t="inlineStr">
+        <is>
+          <t>Día 1</t>
+        </is>
+      </c>
+      <c r="F29" s="32" t="n"/>
+      <c r="G29" s="33" t="n"/>
+      <c r="H29" s="34">
+        <f>IF($E$3="","",$E$3+1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="10" t="n">
         <v>8</v>
       </c>
-      <c r="B27" s="11" t="inlineStr">
+      <c r="B30" s="11" t="inlineStr">
         <is>
           <t>Formación en igualdad (si aplica según plantilla)</t>
         </is>
       </c>
-      <c r="C27" s="16" t="inlineStr">
-        <is>
-          <t>FORMACIÓN OBLI</t>
-        </is>
-      </c>
-      <c r="D27" s="7" t="n"/>
-      <c r="E27" s="13" t="n"/>
-      <c r="F27" s="14" t="n"/>
-      <c r="G27" s="15" t="n"/>
-    </row>
-    <row r="28"/>
-    <row r="29">
-      <c r="A29" s="8" t="inlineStr">
+      <c r="C30" s="16" t="inlineStr">
+        <is>
+          <t>FORMACIÓN OBLIGATORIA</t>
+        </is>
+      </c>
+      <c r="D30" s="28" t="n"/>
+      <c r="E30" s="31" t="inlineStr">
+        <is>
+          <t>Día 30</t>
+        </is>
+      </c>
+      <c r="F30" s="32" t="n"/>
+      <c r="G30" s="33" t="n"/>
+      <c r="H30" s="34">
+        <f>IF($E$3="","",$E$3+30)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31"/>
+    <row r="32">
+      <c r="A32" s="39" t="inlineStr">
         <is>
           <t>👕 EQUIPAMIENTO Y ACCESOS</t>
         </is>
       </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="9" t="inlineStr">
+      <c r="B32" s="40" t="n"/>
+      <c r="C32" s="40" t="n"/>
+      <c r="D32" s="40" t="n"/>
+      <c r="E32" s="40" t="n"/>
+      <c r="F32" s="40" t="n"/>
+      <c r="G32" s="40" t="n"/>
+      <c r="H32" s="40" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="9" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B30" s="9" t="inlineStr">
+      <c r="B33" s="9" t="inlineStr">
         <is>
           <t>Tarea</t>
         </is>
       </c>
-      <c r="C30" s="9" t="inlineStr">
+      <c r="C33" s="9" t="inlineStr">
         <is>
           <t>Categoría</t>
         </is>
       </c>
-      <c r="D30" s="9" t="inlineStr">
+      <c r="D33" s="9" t="inlineStr">
         <is>
           <t>Responsable</t>
         </is>
       </c>
-      <c r="E30" s="9" t="inlineStr">
-        <is>
-          <t>Fecha Límite</t>
-        </is>
-      </c>
-      <c r="F30" s="9" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="G30" s="9" t="inlineStr">
+      <c r="E33" s="9" t="inlineStr">
+        <is>
+          <t>Plazo</t>
+        </is>
+      </c>
+      <c r="F33" s="9" t="inlineStr">
+        <is>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="G33" s="9" t="inlineStr">
         <is>
           <t>Notas</t>
         </is>
       </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="B31" s="11" t="inlineStr">
-        <is>
-          <t>Uniforme completo entregado (tallas verificadas)</t>
-        </is>
-      </c>
-      <c r="C31" s="17" t="inlineStr">
-        <is>
-          <t>EQUIPAMIENTO Y</t>
-        </is>
-      </c>
-      <c r="D31" s="7" t="n"/>
-      <c r="E31" s="13" t="n"/>
-      <c r="F31" s="14" t="n"/>
-      <c r="G31" s="15" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="B32" s="11" t="inlineStr">
-        <is>
-          <t>Calzado de seguridad antideslizante</t>
-        </is>
-      </c>
-      <c r="C32" s="17" t="inlineStr">
-        <is>
-          <t>EQUIPAMIENTO Y</t>
-        </is>
-      </c>
-      <c r="D32" s="7" t="n"/>
-      <c r="E32" s="13" t="n"/>
-      <c r="F32" s="14" t="n"/>
-      <c r="G32" s="15" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="B33" s="11" t="inlineStr">
-        <is>
-          <t>Taquilla asignada con llave/candado</t>
-        </is>
-      </c>
-      <c r="C33" s="17" t="inlineStr">
-        <is>
-          <t>EQUIPAMIENTO Y</t>
-        </is>
-      </c>
-      <c r="D33" s="7" t="n"/>
-      <c r="E33" s="13" t="n"/>
-      <c r="F33" s="14" t="n"/>
-      <c r="G33" s="15" t="n"/>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Fecha límite</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="10" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B34" s="11" t="inlineStr">
         <is>
-          <t>Llaves / tarjeta de acceso al local</t>
-        </is>
-      </c>
-      <c r="C34" s="17" t="inlineStr">
-        <is>
-          <t>EQUIPAMIENTO Y</t>
-        </is>
-      </c>
-      <c r="D34" s="7" t="n"/>
-      <c r="E34" s="13" t="n"/>
-      <c r="F34" s="14" t="n"/>
-      <c r="G34" s="15" t="n"/>
+          <t>Uniforme completo entregado (tallas verificadas)</t>
+        </is>
+      </c>
+      <c r="C34" s="41" t="inlineStr">
+        <is>
+          <t>EQUIPAMIENTO Y ACCESOS</t>
+        </is>
+      </c>
+      <c r="D34" s="28" t="n"/>
+      <c r="E34" s="31" t="inlineStr">
+        <is>
+          <t>Día 1</t>
+        </is>
+      </c>
+      <c r="F34" s="32" t="n"/>
+      <c r="G34" s="33" t="n"/>
+      <c r="H34" s="34">
+        <f>IF($E$3="","",$E$3+1)</f>
+        <v/>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="10" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t>Código alarma comunicado</t>
-        </is>
-      </c>
-      <c r="C35" s="17" t="inlineStr">
-        <is>
-          <t>EQUIPAMIENTO Y</t>
-        </is>
-      </c>
-      <c r="D35" s="7" t="n"/>
-      <c r="E35" s="13" t="n"/>
-      <c r="F35" s="14" t="n"/>
-      <c r="G35" s="15" t="n"/>
+          <t>Calzado de seguridad antideslizante</t>
+        </is>
+      </c>
+      <c r="C35" s="41" t="inlineStr">
+        <is>
+          <t>EQUIPAMIENTO Y ACCESOS</t>
+        </is>
+      </c>
+      <c r="D35" s="28" t="n"/>
+      <c r="E35" s="31" t="inlineStr">
+        <is>
+          <t>Día 1</t>
+        </is>
+      </c>
+      <c r="F35" s="32" t="n"/>
+      <c r="G35" s="33" t="n"/>
+      <c r="H35" s="34">
+        <f>IF($E$3="","",$E$3+1)</f>
+        <v/>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="10" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B36" s="11" t="inlineStr">
         <is>
-          <t>Acceso sistema TPV / caja registradora</t>
-        </is>
-      </c>
-      <c r="C36" s="17" t="inlineStr">
-        <is>
-          <t>EQUIPAMIENTO Y</t>
-        </is>
-      </c>
-      <c r="D36" s="7" t="n"/>
-      <c r="E36" s="13" t="n"/>
-      <c r="F36" s="14" t="n"/>
-      <c r="G36" s="15" t="n"/>
+          <t>Taquilla asignada con llave/candado</t>
+        </is>
+      </c>
+      <c r="C36" s="41" t="inlineStr">
+        <is>
+          <t>EQUIPAMIENTO Y ACCESOS</t>
+        </is>
+      </c>
+      <c r="D36" s="28" t="n"/>
+      <c r="E36" s="31" t="inlineStr">
+        <is>
+          <t>Día 1</t>
+        </is>
+      </c>
+      <c r="F36" s="32" t="n"/>
+      <c r="G36" s="33" t="n"/>
+      <c r="H36" s="34">
+        <f>IF($E$3="","",$E$3+1)</f>
+        <v/>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="10" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>Acceso herramientas digitales (email, app turnos, etc.)</t>
-        </is>
-      </c>
-      <c r="C37" s="17" t="inlineStr">
-        <is>
-          <t>EQUIPAMIENTO Y</t>
-        </is>
-      </c>
-      <c r="D37" s="7" t="n"/>
-      <c r="E37" s="13" t="n"/>
-      <c r="F37" s="14" t="n"/>
-      <c r="G37" s="15" t="n"/>
+          <t>Llaves / tarjeta de acceso al local</t>
+        </is>
+      </c>
+      <c r="C37" s="41" t="inlineStr">
+        <is>
+          <t>EQUIPAMIENTO Y ACCESOS</t>
+        </is>
+      </c>
+      <c r="D37" s="28" t="n"/>
+      <c r="E37" s="31" t="inlineStr">
+        <is>
+          <t>Día 1</t>
+        </is>
+      </c>
+      <c r="F37" s="32" t="n"/>
+      <c r="G37" s="33" t="n"/>
+      <c r="H37" s="34">
+        <f>IF($E$3="","",$E$3+1)</f>
+        <v/>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="10" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B38" s="11" t="inlineStr">
         <is>
-          <t>Placa identificativa / nombre</t>
-        </is>
-      </c>
-      <c r="C38" s="17" t="inlineStr">
-        <is>
-          <t>EQUIPAMIENTO Y</t>
-        </is>
-      </c>
-      <c r="D38" s="7" t="n"/>
-      <c r="E38" s="13" t="n"/>
-      <c r="F38" s="14" t="n"/>
-      <c r="G38" s="15" t="n"/>
+          <t>Código alarma comunicado</t>
+        </is>
+      </c>
+      <c r="C38" s="41" t="inlineStr">
+        <is>
+          <t>EQUIPAMIENTO Y ACCESOS</t>
+        </is>
+      </c>
+      <c r="D38" s="28" t="n"/>
+      <c r="E38" s="31" t="inlineStr">
+        <is>
+          <t>Día 7</t>
+        </is>
+      </c>
+      <c r="F38" s="32" t="n"/>
+      <c r="G38" s="33" t="n"/>
+      <c r="H38" s="34">
+        <f>IF($E$3="","",$E$3+7)</f>
+        <v/>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="B39" s="11" t="inlineStr">
+        <is>
+          <t>Acceso sistema TPV / caja registradora</t>
+        </is>
+      </c>
+      <c r="C39" s="41" t="inlineStr">
+        <is>
+          <t>EQUIPAMIENTO Y ACCESOS</t>
+        </is>
+      </c>
+      <c r="D39" s="28" t="n"/>
+      <c r="E39" s="31" t="inlineStr">
+        <is>
+          <t>Día 1</t>
+        </is>
+      </c>
+      <c r="F39" s="32" t="n"/>
+      <c r="G39" s="33" t="n"/>
+      <c r="H39" s="34">
+        <f>IF($E$3="","",$E$3+1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="B40" s="11" t="inlineStr">
+        <is>
+          <t>Acceso herramientas digitales (email, app turnos, etc.)</t>
+        </is>
+      </c>
+      <c r="C40" s="41" t="inlineStr">
+        <is>
+          <t>EQUIPAMIENTO Y ACCESOS</t>
+        </is>
+      </c>
+      <c r="D40" s="28" t="n"/>
+      <c r="E40" s="31" t="inlineStr">
+        <is>
+          <t>Día 1</t>
+        </is>
+      </c>
+      <c r="F40" s="32" t="n"/>
+      <c r="G40" s="33" t="n"/>
+      <c r="H40" s="34">
+        <f>IF($E$3="","",$E$3+1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="B41" s="11" t="inlineStr">
+        <is>
+          <t>Placa identificativa / nombre</t>
+        </is>
+      </c>
+      <c r="C41" s="41" t="inlineStr">
+        <is>
+          <t>EQUIPAMIENTO Y ACCESOS</t>
+        </is>
+      </c>
+      <c r="D41" s="28" t="n"/>
+      <c r="E41" s="31" t="inlineStr">
+        <is>
+          <t>Día 7</t>
+        </is>
+      </c>
+      <c r="F41" s="32" t="n"/>
+      <c r="G41" s="33" t="n"/>
+      <c r="H41" s="34">
+        <f>IF($E$3="","",$E$3+7)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="10" t="n">
         <v>9</v>
       </c>
-      <c r="B39" s="11" t="inlineStr">
+      <c r="B42" s="11" t="inlineStr">
         <is>
           <t>EPI adicional si aplica (guantes, delantal térmico, etc.)</t>
         </is>
       </c>
-      <c r="C39" s="17" t="inlineStr">
-        <is>
-          <t>EQUIPAMIENTO Y</t>
-        </is>
-      </c>
-      <c r="D39" s="7" t="n"/>
-      <c r="E39" s="13" t="n"/>
-      <c r="F39" s="14" t="n"/>
-      <c r="G39" s="15" t="n"/>
-    </row>
-    <row r="40"/>
-    <row r="41">
-      <c r="A41" s="8" t="inlineStr">
+      <c r="C42" s="41" t="inlineStr">
+        <is>
+          <t>EQUIPAMIENTO Y ACCESOS</t>
+        </is>
+      </c>
+      <c r="D42" s="28" t="n"/>
+      <c r="E42" s="31" t="inlineStr">
+        <is>
+          <t>Día 1</t>
+        </is>
+      </c>
+      <c r="F42" s="32" t="n"/>
+      <c r="G42" s="33" t="n"/>
+      <c r="H42" s="34">
+        <f>IF($E$3="","",$E$3+1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43"/>
+    <row r="44">
+      <c r="A44" s="42" t="inlineStr">
         <is>
           <t>🏢 FORMACIÓN OPERATIVA</t>
         </is>
       </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="9" t="inlineStr">
+      <c r="B44" s="43" t="n"/>
+      <c r="C44" s="43" t="n"/>
+      <c r="D44" s="43" t="n"/>
+      <c r="E44" s="43" t="n"/>
+      <c r="F44" s="43" t="n"/>
+      <c r="G44" s="43" t="n"/>
+      <c r="H44" s="43" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="9" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B42" s="9" t="inlineStr">
+      <c r="B45" s="9" t="inlineStr">
         <is>
           <t>Tarea</t>
         </is>
       </c>
-      <c r="C42" s="9" t="inlineStr">
+      <c r="C45" s="9" t="inlineStr">
         <is>
           <t>Categoría</t>
         </is>
       </c>
-      <c r="D42" s="9" t="inlineStr">
+      <c r="D45" s="9" t="inlineStr">
         <is>
           <t>Responsable</t>
         </is>
       </c>
-      <c r="E42" s="9" t="inlineStr">
-        <is>
-          <t>Fecha Límite</t>
-        </is>
-      </c>
-      <c r="F42" s="9" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="G42" s="9" t="inlineStr">
+      <c r="E45" s="9" t="inlineStr">
+        <is>
+          <t>Plazo</t>
+        </is>
+      </c>
+      <c r="F45" s="9" t="inlineStr">
+        <is>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="G45" s="9" t="inlineStr">
         <is>
           <t>Notas</t>
         </is>
       </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="B43" s="11" t="inlineStr">
-        <is>
-          <t>Tour completo de instalaciones</t>
-        </is>
-      </c>
-      <c r="C43" s="18" t="inlineStr">
-        <is>
-          <t>FORMACIÓN OPER</t>
-        </is>
-      </c>
-      <c r="D43" s="7" t="n"/>
-      <c r="E43" s="13" t="n"/>
-      <c r="F43" s="14" t="n"/>
-      <c r="G43" s="15" t="n"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="B44" s="11" t="inlineStr">
-        <is>
-          <t>Presentación al equipo y responsables directos</t>
-        </is>
-      </c>
-      <c r="C44" s="18" t="inlineStr">
-        <is>
-          <t>FORMACIÓN OPER</t>
-        </is>
-      </c>
-      <c r="D44" s="7" t="n"/>
-      <c r="E44" s="13" t="n"/>
-      <c r="F44" s="14" t="n"/>
-      <c r="G44" s="15" t="n"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="B45" s="11" t="inlineStr">
-        <is>
-          <t>Manual del puesto entregado y explicado</t>
-        </is>
-      </c>
-      <c r="C45" s="18" t="inlineStr">
-        <is>
-          <t>FORMACIÓN OPER</t>
-        </is>
-      </c>
-      <c r="D45" s="7" t="n"/>
-      <c r="E45" s="13" t="n"/>
-      <c r="F45" s="14" t="n"/>
-      <c r="G45" s="15" t="n"/>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Fecha límite</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="10" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B46" s="11" t="inlineStr">
         <is>
-          <t>Protocolo de limpieza y desinfección</t>
+          <t>Tour completo de instalaciones</t>
         </is>
       </c>
       <c r="C46" s="18" t="inlineStr">
         <is>
-          <t>FORMACIÓN OPER</t>
-        </is>
-      </c>
-      <c r="D46" s="7" t="n"/>
-      <c r="E46" s="13" t="n"/>
-      <c r="F46" s="14" t="n"/>
-      <c r="G46" s="15" t="n"/>
+          <t>FORMACIÓN OPERATIVA</t>
+        </is>
+      </c>
+      <c r="D46" s="28" t="n"/>
+      <c r="E46" s="31" t="inlineStr">
+        <is>
+          <t>Día 1</t>
+        </is>
+      </c>
+      <c r="F46" s="32" t="n"/>
+      <c r="G46" s="33" t="n"/>
+      <c r="H46" s="34">
+        <f>IF($E$3="","",$E$3+1)</f>
+        <v/>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="10" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t>Sistema de caja / TPV — práctica supervisada</t>
+          <t>Presentación al equipo y responsables directos</t>
         </is>
       </c>
       <c r="C47" s="18" t="inlineStr">
         <is>
-          <t>FORMACIÓN OPER</t>
-        </is>
-      </c>
-      <c r="D47" s="7" t="n"/>
-      <c r="E47" s="13" t="n"/>
-      <c r="F47" s="14" t="n"/>
-      <c r="G47" s="15" t="n"/>
+          <t>FORMACIÓN OPERATIVA</t>
+        </is>
+      </c>
+      <c r="D47" s="28" t="n"/>
+      <c r="E47" s="31" t="inlineStr">
+        <is>
+          <t>Día 1</t>
+        </is>
+      </c>
+      <c r="F47" s="32" t="n"/>
+      <c r="G47" s="33" t="n"/>
+      <c r="H47" s="34">
+        <f>IF($E$3="","",$E$3+1)</f>
+        <v/>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="10" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B48" s="11" t="inlineStr">
         <is>
-          <t>Carta / menú — estudio y degustación</t>
+          <t>Manual del puesto entregado y explicado</t>
         </is>
       </c>
       <c r="C48" s="18" t="inlineStr">
         <is>
-          <t>FORMACIÓN OPER</t>
-        </is>
-      </c>
-      <c r="D48" s="7" t="n"/>
-      <c r="E48" s="13" t="n"/>
-      <c r="F48" s="14" t="n"/>
-      <c r="G48" s="15" t="n"/>
+          <t>FORMACIÓN OPERATIVA</t>
+        </is>
+      </c>
+      <c r="D48" s="28" t="n"/>
+      <c r="E48" s="31" t="inlineStr">
+        <is>
+          <t>Día 1</t>
+        </is>
+      </c>
+      <c r="F48" s="32" t="n"/>
+      <c r="G48" s="33" t="n"/>
+      <c r="H48" s="34">
+        <f>IF($E$3="","",$E$3+1)</f>
+        <v/>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="10" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t>Protocolo de atención al cliente</t>
+          <t>Protocolo de limpieza y desinfección</t>
         </is>
       </c>
       <c r="C49" s="18" t="inlineStr">
         <is>
-          <t>FORMACIÓN OPER</t>
-        </is>
-      </c>
-      <c r="D49" s="7" t="n"/>
-      <c r="E49" s="13" t="n"/>
-      <c r="F49" s="14" t="n"/>
-      <c r="G49" s="15" t="n"/>
+          <t>FORMACIÓN OPERATIVA</t>
+        </is>
+      </c>
+      <c r="D49" s="28" t="n"/>
+      <c r="E49" s="31" t="inlineStr">
+        <is>
+          <t>Día 1</t>
+        </is>
+      </c>
+      <c r="F49" s="32" t="n"/>
+      <c r="G49" s="33" t="n"/>
+      <c r="H49" s="34">
+        <f>IF($E$3="","",$E$3+1)</f>
+        <v/>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="10" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B50" s="11" t="inlineStr">
         <is>
-          <t>Sistema de reservas (si aplica)</t>
+          <t>Sistema de caja / TPV — práctica supervisada</t>
         </is>
       </c>
       <c r="C50" s="18" t="inlineStr">
         <is>
-          <t>FORMACIÓN OPER</t>
-        </is>
-      </c>
-      <c r="D50" s="7" t="n"/>
-      <c r="E50" s="13" t="n"/>
-      <c r="F50" s="14" t="n"/>
-      <c r="G50" s="15" t="n"/>
+          <t>FORMACIÓN OPERATIVA</t>
+        </is>
+      </c>
+      <c r="D50" s="28" t="n"/>
+      <c r="E50" s="31" t="inlineStr">
+        <is>
+          <t>Día 7</t>
+        </is>
+      </c>
+      <c r="F50" s="32" t="n"/>
+      <c r="G50" s="33" t="n"/>
+      <c r="H50" s="34">
+        <f>IF($E$3="","",$E$3+7)</f>
+        <v/>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="10" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>Protocolo de aperturas y cierres</t>
+          <t>Carta / menú — estudio y degustación</t>
         </is>
       </c>
       <c r="C51" s="18" t="inlineStr">
         <is>
-          <t>FORMACIÓN OPER</t>
-        </is>
-      </c>
-      <c r="D51" s="7" t="n"/>
-      <c r="E51" s="13" t="n"/>
-      <c r="F51" s="14" t="n"/>
-      <c r="G51" s="15" t="n"/>
+          <t>FORMACIÓN OPERATIVA</t>
+        </is>
+      </c>
+      <c r="D51" s="28" t="n"/>
+      <c r="E51" s="31" t="inlineStr">
+        <is>
+          <t>Día 7</t>
+        </is>
+      </c>
+      <c r="F51" s="32" t="n"/>
+      <c r="G51" s="33" t="n"/>
+      <c r="H51" s="34">
+        <f>IF($E$3="","",$E$3+7)</f>
+        <v/>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="10" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B52" s="11" t="inlineStr">
         <is>
-          <t>Gestión de residuos y reciclaje</t>
+          <t>Protocolo de atención al cliente</t>
         </is>
       </c>
       <c r="C52" s="18" t="inlineStr">
         <is>
-          <t>FORMACIÓN OPER</t>
-        </is>
-      </c>
-      <c r="D52" s="7" t="n"/>
-      <c r="E52" s="13" t="n"/>
-      <c r="F52" s="14" t="n"/>
-      <c r="G52" s="15" t="n"/>
+          <t>FORMACIÓN OPERATIVA</t>
+        </is>
+      </c>
+      <c r="D52" s="28" t="n"/>
+      <c r="E52" s="31" t="inlineStr">
+        <is>
+          <t>Día 7</t>
+        </is>
+      </c>
+      <c r="F52" s="32" t="n"/>
+      <c r="G52" s="33" t="n"/>
+      <c r="H52" s="34">
+        <f>IF($E$3="","",$E$3+7)</f>
+        <v/>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="10" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B53" s="11" t="inlineStr">
         <is>
-          <t>Sistema de pedidos a proveedores (si aplica)</t>
+          <t>Sistema de reservas (si aplica)</t>
         </is>
       </c>
       <c r="C53" s="18" t="inlineStr">
         <is>
-          <t>FORMACIÓN OPER</t>
-        </is>
-      </c>
-      <c r="D53" s="7" t="n"/>
-      <c r="E53" s="13" t="n"/>
-      <c r="F53" s="14" t="n"/>
-      <c r="G53" s="15" t="n"/>
+          <t>FORMACIÓN OPERATIVA</t>
+        </is>
+      </c>
+      <c r="D53" s="28" t="n"/>
+      <c r="E53" s="31" t="inlineStr">
+        <is>
+          <t>Día 7</t>
+        </is>
+      </c>
+      <c r="F53" s="32" t="n"/>
+      <c r="G53" s="33" t="n"/>
+      <c r="H53" s="34">
+        <f>IF($E$3="","",$E$3+7)</f>
+        <v/>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B54" s="11" t="inlineStr">
+        <is>
+          <t>Protocolo de aperturas y cierres</t>
+        </is>
+      </c>
+      <c r="C54" s="18" t="inlineStr">
+        <is>
+          <t>FORMACIÓN OPERATIVA</t>
+        </is>
+      </c>
+      <c r="D54" s="28" t="n"/>
+      <c r="E54" s="31" t="inlineStr">
+        <is>
+          <t>Día 7</t>
+        </is>
+      </c>
+      <c r="F54" s="32" t="n"/>
+      <c r="G54" s="33" t="n"/>
+      <c r="H54" s="34">
+        <f>IF($E$3="","",$E$3+7)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="B55" s="11" t="inlineStr">
+        <is>
+          <t>Gestión de residuos y reciclaje</t>
+        </is>
+      </c>
+      <c r="C55" s="18" t="inlineStr">
+        <is>
+          <t>FORMACIÓN OPERATIVA</t>
+        </is>
+      </c>
+      <c r="D55" s="28" t="n"/>
+      <c r="E55" s="31" t="inlineStr">
+        <is>
+          <t>Día 7</t>
+        </is>
+      </c>
+      <c r="F55" s="32" t="n"/>
+      <c r="G55" s="33" t="n"/>
+      <c r="H55" s="34">
+        <f>IF($E$3="","",$E$3+7)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="10" t="n">
+        <v>11</v>
+      </c>
+      <c r="B56" s="11" t="inlineStr">
+        <is>
+          <t>Sistema de pedidos a proveedores (si aplica)</t>
+        </is>
+      </c>
+      <c r="C56" s="18" t="inlineStr">
+        <is>
+          <t>FORMACIÓN OPERATIVA</t>
+        </is>
+      </c>
+      <c r="D56" s="28" t="n"/>
+      <c r="E56" s="31" t="inlineStr">
+        <is>
+          <t>Día 30</t>
+        </is>
+      </c>
+      <c r="F56" s="32" t="n"/>
+      <c r="G56" s="33" t="n"/>
+      <c r="H56" s="34">
+        <f>IF($E$3="","",$E$3+30)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="10" t="n">
         <v>12</v>
       </c>
-      <c r="B54" s="11" t="inlineStr">
+      <c r="B57" s="11" t="inlineStr">
         <is>
           <t>Protocolo de quejas y reclamaciones</t>
         </is>
       </c>
-      <c r="C54" s="18" t="inlineStr">
-        <is>
-          <t>FORMACIÓN OPER</t>
-        </is>
-      </c>
-      <c r="D54" s="7" t="n"/>
-      <c r="E54" s="13" t="n"/>
-      <c r="F54" s="14" t="n"/>
-      <c r="G54" s="15" t="n"/>
-    </row>
-    <row r="55"/>
-    <row r="56">
-      <c r="A56" s="8" t="inlineStr">
+      <c r="C57" s="18" t="inlineStr">
+        <is>
+          <t>FORMACIÓN OPERATIVA</t>
+        </is>
+      </c>
+      <c r="D57" s="28" t="n"/>
+      <c r="E57" s="31" t="inlineStr">
+        <is>
+          <t>Día 30</t>
+        </is>
+      </c>
+      <c r="F57" s="32" t="n"/>
+      <c r="G57" s="33" t="n"/>
+      <c r="H57" s="34">
+        <f>IF($E$3="","",$E$3+30)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58"/>
+    <row r="59">
+      <c r="A59" s="44" t="inlineStr">
         <is>
           <t>📊 PERIODO DE PRUEBA Y EVALUACIÓN</t>
         </is>
       </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="9" t="inlineStr">
+      <c r="B59" s="45" t="n"/>
+      <c r="C59" s="45" t="n"/>
+      <c r="D59" s="45" t="n"/>
+      <c r="E59" s="45" t="n"/>
+      <c r="F59" s="45" t="n"/>
+      <c r="G59" s="45" t="n"/>
+      <c r="H59" s="45" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="9" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B57" s="9" t="inlineStr">
+      <c r="B60" s="9" t="inlineStr">
         <is>
           <t>Tarea</t>
         </is>
       </c>
-      <c r="C57" s="9" t="inlineStr">
+      <c r="C60" s="9" t="inlineStr">
         <is>
           <t>Categoría</t>
         </is>
       </c>
-      <c r="D57" s="9" t="inlineStr">
+      <c r="D60" s="9" t="inlineStr">
         <is>
           <t>Responsable</t>
         </is>
       </c>
-      <c r="E57" s="9" t="inlineStr">
-        <is>
-          <t>Fecha Límite</t>
-        </is>
-      </c>
-      <c r="F57" s="9" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="G57" s="9" t="inlineStr">
+      <c r="E60" s="9" t="inlineStr">
+        <is>
+          <t>Plazo</t>
+        </is>
+      </c>
+      <c r="F60" s="9" t="inlineStr">
+        <is>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="G60" s="9" t="inlineStr">
         <is>
           <t>Notas</t>
         </is>
       </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="B58" s="11" t="inlineStr">
-        <is>
-          <t>Objetivos semana 1 definidos y comunicados</t>
-        </is>
-      </c>
-      <c r="C58" s="19" t="inlineStr">
-        <is>
-          <t>PERIODO DE PRU</t>
-        </is>
-      </c>
-      <c r="D58" s="7" t="n"/>
-      <c r="E58" s="13" t="n"/>
-      <c r="F58" s="14" t="n"/>
-      <c r="G58" s="15" t="n"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="B59" s="11" t="inlineStr">
-        <is>
-          <t>Objetivos semana 2 definidos y comunicados</t>
-        </is>
-      </c>
-      <c r="C59" s="19" t="inlineStr">
-        <is>
-          <t>PERIODO DE PRU</t>
-        </is>
-      </c>
-      <c r="D59" s="7" t="n"/>
-      <c r="E59" s="13" t="n"/>
-      <c r="F59" s="14" t="n"/>
-      <c r="G59" s="15" t="n"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="B60" s="11" t="inlineStr">
-        <is>
-          <t>Objetivos semana 4 (primer mes) definidos</t>
-        </is>
-      </c>
-      <c r="C60" s="19" t="inlineStr">
-        <is>
-          <t>PERIODO DE PRU</t>
-        </is>
-      </c>
-      <c r="D60" s="7" t="n"/>
-      <c r="E60" s="13" t="n"/>
-      <c r="F60" s="14" t="n"/>
-      <c r="G60" s="15" t="n"/>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Fecha límite</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="10" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B61" s="11" t="inlineStr">
         <is>
-          <t>Evaluación informal día 3 — primeras impresiones</t>
+          <t>Objetivos semana 1 definidos y comunicados</t>
         </is>
       </c>
       <c r="C61" s="19" t="inlineStr">
         <is>
-          <t>PERIODO DE PRU</t>
-        </is>
-      </c>
-      <c r="D61" s="7" t="n"/>
-      <c r="E61" s="13" t="n"/>
-      <c r="F61" s="14" t="n"/>
-      <c r="G61" s="15" t="n"/>
+          <t>PERIODO DE PRUEBA</t>
+        </is>
+      </c>
+      <c r="D61" s="28" t="n"/>
+      <c r="E61" s="31" t="inlineStr">
+        <is>
+          <t>Día 1</t>
+        </is>
+      </c>
+      <c r="F61" s="32" t="n"/>
+      <c r="G61" s="33" t="n"/>
+      <c r="H61" s="34">
+        <f>IF($E$3="","",$E$3+1)</f>
+        <v/>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="10" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B62" s="11" t="inlineStr">
         <is>
-          <t>Evaluación formal día 15 — revisión intermedia</t>
+          <t>Objetivos semana 2 definidos y comunicados</t>
         </is>
       </c>
       <c r="C62" s="19" t="inlineStr">
         <is>
-          <t>PERIODO DE PRU</t>
-        </is>
-      </c>
-      <c r="D62" s="7" t="n"/>
-      <c r="E62" s="13" t="n"/>
-      <c r="F62" s="14" t="n"/>
-      <c r="G62" s="15" t="n"/>
+          <t>PERIODO DE PRUEBA</t>
+        </is>
+      </c>
+      <c r="D62" s="28" t="n"/>
+      <c r="E62" s="31" t="inlineStr">
+        <is>
+          <t>Día 7</t>
+        </is>
+      </c>
+      <c r="F62" s="32" t="n"/>
+      <c r="G62" s="33" t="n"/>
+      <c r="H62" s="34">
+        <f>IF($E$3="","",$E$3+7)</f>
+        <v/>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="10" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B63" s="11" t="inlineStr">
         <is>
-          <t>Evaluación formal día 30 — decisión continuidad</t>
+          <t>Objetivos semana 4 (primer mes) definidos</t>
         </is>
       </c>
       <c r="C63" s="19" t="inlineStr">
         <is>
-          <t>PERIODO DE PRU</t>
-        </is>
-      </c>
-      <c r="D63" s="7" t="n"/>
-      <c r="E63" s="13" t="n"/>
-      <c r="F63" s="14" t="n"/>
-      <c r="G63" s="15" t="n"/>
+          <t>PERIODO DE PRUEBA</t>
+        </is>
+      </c>
+      <c r="D63" s="28" t="n"/>
+      <c r="E63" s="31" t="inlineStr">
+        <is>
+          <t>Día 30</t>
+        </is>
+      </c>
+      <c r="F63" s="32" t="n"/>
+      <c r="G63" s="33" t="n"/>
+      <c r="H63" s="34">
+        <f>IF($E$3="","",$E$3+30)</f>
+        <v/>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="10" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B64" s="11" t="inlineStr">
         <is>
-          <t>Feedback del equipo recogido</t>
+          <t>Evaluación informal día 3 — primeras impresiones</t>
         </is>
       </c>
       <c r="C64" s="19" t="inlineStr">
         <is>
-          <t>PERIODO DE PRU</t>
-        </is>
-      </c>
-      <c r="D64" s="7" t="n"/>
-      <c r="E64" s="13" t="n"/>
-      <c r="F64" s="14" t="n"/>
-      <c r="G64" s="15" t="n"/>
+          <t>PERIODO DE PRUEBA</t>
+        </is>
+      </c>
+      <c r="D64" s="28" t="n"/>
+      <c r="E64" s="31" t="inlineStr">
+        <is>
+          <t>Día 3</t>
+        </is>
+      </c>
+      <c r="F64" s="32" t="n"/>
+      <c r="G64" s="33" t="n"/>
+      <c r="H64" s="34">
+        <f>IF($E$3="","",$E$3+3)</f>
+        <v/>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="B65" s="11" t="inlineStr">
+        <is>
+          <t>Evaluación formal día 15 — revisión intermedia</t>
+        </is>
+      </c>
+      <c r="C65" s="19" t="inlineStr">
+        <is>
+          <t>PERIODO DE PRUEBA</t>
+        </is>
+      </c>
+      <c r="D65" s="28" t="n"/>
+      <c r="E65" s="31" t="inlineStr">
+        <is>
+          <t>Día 15</t>
+        </is>
+      </c>
+      <c r="F65" s="32" t="n"/>
+      <c r="G65" s="33" t="n"/>
+      <c r="H65" s="34">
+        <f>IF($E$3="","",$E$3+15)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="B66" s="11" t="inlineStr">
+        <is>
+          <t>Evaluación formal día 30 — decisión continuidad</t>
+        </is>
+      </c>
+      <c r="C66" s="19" t="inlineStr">
+        <is>
+          <t>PERIODO DE PRUEBA</t>
+        </is>
+      </c>
+      <c r="D66" s="28" t="n"/>
+      <c r="E66" s="31" t="inlineStr">
+        <is>
+          <t>Día 30</t>
+        </is>
+      </c>
+      <c r="F66" s="32" t="n"/>
+      <c r="G66" s="33" t="n"/>
+      <c r="H66" s="34">
+        <f>IF($E$3="","",$E$3+30)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="B67" s="11" t="inlineStr">
+        <is>
+          <t>Feedback del equipo recogido</t>
+        </is>
+      </c>
+      <c r="C67" s="19" t="inlineStr">
+        <is>
+          <t>PERIODO DE PRUEBA</t>
+        </is>
+      </c>
+      <c r="D67" s="28" t="n"/>
+      <c r="E67" s="31" t="inlineStr">
+        <is>
+          <t>Día 30</t>
+        </is>
+      </c>
+      <c r="F67" s="32" t="n"/>
+      <c r="G67" s="33" t="n"/>
+      <c r="H67" s="34">
+        <f>IF($E$3="","",$E$3+30)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="10" t="n">
         <v>8</v>
       </c>
-      <c r="B65" s="11" t="inlineStr">
+      <c r="B68" s="11" t="inlineStr">
         <is>
           <t>Plan de desarrollo si se confirma en puesto</t>
         </is>
       </c>
-      <c r="C65" s="19" t="inlineStr">
-        <is>
-          <t>PERIODO DE PRU</t>
-        </is>
-      </c>
-      <c r="D65" s="7" t="n"/>
-      <c r="E65" s="13" t="n"/>
-      <c r="F65" s="14" t="n"/>
-      <c r="G65" s="15" t="n"/>
-    </row>
-    <row r="66"/>
-    <row r="67">
-      <c r="A67" s="8" t="inlineStr">
+      <c r="C68" s="19" t="inlineStr">
+        <is>
+          <t>PERIODO DE PRUEBA</t>
+        </is>
+      </c>
+      <c r="D68" s="28" t="n"/>
+      <c r="E68" s="31" t="inlineStr">
+        <is>
+          <t>Día 30</t>
+        </is>
+      </c>
+      <c r="F68" s="32" t="n"/>
+      <c r="G68" s="33" t="n"/>
+      <c r="H68" s="34">
+        <f>IF($E$3="","",$E$3+30)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="69"/>
+    <row r="70">
+      <c r="A70" s="46" t="inlineStr">
         <is>
           <t>RESUMEN</t>
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="B68" s="6" t="inlineStr">
-        <is>
-          <t>Total tareas completadas:</t>
-        </is>
-      </c>
-      <c r="C68" s="20">
-        <f>COUNTIF(F7:F65,"✓")</f>
-        <v>4.0</v>
-      </c>
-      <c r="D68" t="inlineStr">
+    <row r="71">
+      <c r="B71" s="47" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="C71" s="48">
+        <f>COUNTIF($F$7:$F$19,"✓")+COUNTIF($F$23:$F$30,"✓")+COUNTIF($F$34:$F$42,"✓")+COUNTIF($F$46:$F$57,"✓")+COUNTIF($F$61:$F$68,"✓")</f>
+        <v>0.0</v>
+      </c>
+      <c r="D71" t="inlineStr">
         <is>
           <t>de</t>
         </is>
       </c>
-      <c r="E68">
-        <f>COUNTIF(B7:B65,"?*")</f>
-        <v>51.0</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="B69" s="6" t="inlineStr">
-        <is>
-          <t>Total tareas:</t>
-        </is>
-      </c>
-      <c r="C69" s="21" t="n">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="B70" s="6" t="inlineStr">
-        <is>
-          <t>Progreso (%):</t>
-        </is>
-      </c>
-      <c r="C70" s="22">
-        <f>IF(C69&gt;0,C68/C69*100,0)</f>
-        <v>8.51063829787234</v>
-      </c>
-    </row>
-    <row r="71"/>
+      <c r="E71" s="49">
+        <f>COUNTIF($B$7:$B$19,"?*")+COUNTIF($B$23:$B$30,"?*")+COUNTIF($B$34:$B$42,"?*")+COUNTIF($B$46:$B$57,"?*")+COUNTIF($B$61:$B$68,"?*")</f>
+        <v>50.0</v>
+      </c>
+    </row>
     <row r="72">
-      <c r="A72" s="23" t="inlineStr">
+      <c r="B72" s="47" t="inlineStr">
+        <is>
+          <t>Total tareas aplicables (sin las marcadas «—»):</t>
+        </is>
+      </c>
+      <c r="C72" s="50">
+        <f>$E$71-(COUNTIF($F$7:$F$19,"—")+COUNTIF($F$23:$F$30,"—")+COUNTIF($F$34:$F$42,"—")+COUNTIF($F$46:$F$57,"—")+COUNTIF($F$61:$F$68,"—"))</f>
+        <v>50.0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="B73" s="47" t="inlineStr">
+        <is>
+          <t>Progreso:</t>
+        </is>
+      </c>
+      <c r="C73" s="51">
+        <f>IF($C$72&gt;0,$C$71/$C$72,0)</f>
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="74"/>
+    <row r="75">
+      <c r="A75" s="23" t="inlineStr">
         <is>
           <t>Firma responsable: _________________  Fecha: ___/___/______</t>
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="23" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="23" t="inlineStr">
         <is>
           <t>© 2026 AI Chef Pro · aichef.pro</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
   <mergeCells count="9">
+    <mergeCell ref="A44:G44"/>
+    <mergeCell ref="A76:G76"/>
     <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A32:G32"/>
+    <mergeCell ref="A21:G21"/>
+    <mergeCell ref="A59:G59"/>
+    <mergeCell ref="A5:G5"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A18:G18"/>
-    <mergeCell ref="A72:G72"/>
-    <mergeCell ref="A41:G41"/>
-    <mergeCell ref="A73:G73"/>
-    <mergeCell ref="A56:G56"/>
-    <mergeCell ref="A5:G5"/>
-    <mergeCell ref="A29:G29"/>
+    <mergeCell ref="A75:G75"/>
   </mergeCells>
-  <conditionalFormatting sqref="A7:G65">
+  <conditionalFormatting sqref="A7:H68">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$F7="✓"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F7 F8 F9 F10 F11 F12 F13 F14 F15 F16 F20 F21 F22 F23 F24 F25 F26 F27 F31 F32 F33 F34 F35 F36 F37 F38 F39 F43 F44 F45 F46 F47 F48 F49 F50 F51 F52 F53 F54 F58 F59 F60 F61 F62 F63 F64 F65" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F7:F19 F23:F30 F34:F42 F46:F57 F61:F68" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="✓ hecha · ✗ pendiente · — no aplica a este puesto." promptTitle="kitgp-v2b · Hecho" prompt="Marca «—» en lo que NO aplique a este puesto (un cocinero de partida no necesita el acceso al TPV): esas tareas salen del denominador y el progreso puede llegar al 100 %." type="list" errorStyle="stop">
       <formula1>"✓,✗,—"</formula1>
     </dataValidation>
   </dataValidations>
